--- a/VTRS.xlsx
+++ b/VTRS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFE4CEC-2C67-4AFE-9C72-5171EDBE4039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408415BD-06B4-4228-AEC7-56DBEF78FC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58740" yWindow="2640" windowWidth="19870" windowHeight="18080" xr2:uid="{813BBC27-F478-46C7-9133-423B20FE42FB}"/>
+    <workbookView xWindow="20880" yWindow="3490" windowWidth="19050" windowHeight="16100" xr2:uid="{813BBC27-F478-46C7-9133-423B20FE42FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2395,7 +2395,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="338">
   <si>
     <t>Price</t>
   </si>
@@ -3406,6 +3406,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -4203,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>8.32</v>
+        <v>17.649999999999999</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
@@ -4211,10 +4214,10 @@
         <v>1</v>
       </c>
       <c r="M3" s="2">
-        <v>1173.6819640000001</v>
+        <v>1164.5526540000001</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
@@ -4223,7 +4226,7 @@
       </c>
       <c r="M4" s="2">
         <f>M2*M3</f>
-        <v>9765.0339404800015</v>
+        <v>20554.3543431</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -4232,10 +4235,10 @@
         <v>3</v>
       </c>
       <c r="M5" s="2">
-        <v>755</v>
+        <v>1804.2</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
@@ -4243,10 +4246,11 @@
         <v>4</v>
       </c>
       <c r="M6" s="2">
-        <v>14186</v>
+        <f>12413.5+1931.1</f>
+        <v>14344.6</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
@@ -4255,7 +4259,7 @@
       </c>
       <c r="M7" s="2">
         <f>M4-M5+M6</f>
-        <v>23196.033940480003</v>
+        <v>33094.754343100001</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -4817,19 +4821,19 @@
         <v>388</v>
       </c>
       <c r="X12" s="2">
-        <f>+T12</f>
+        <f t="shared" ref="X12:Z13" si="1">+T12</f>
         <v>348.4</v>
       </c>
       <c r="Y12" s="2">
-        <f>+U12</f>
+        <f t="shared" si="1"/>
         <v>375.6</v>
       </c>
       <c r="Z12" s="2">
-        <f>+V12</f>
+        <f t="shared" si="1"/>
         <v>355.9</v>
       </c>
       <c r="AL12" s="2">
-        <f t="shared" ref="AL12:AL29" si="1">SUM(S12:V12)</f>
+        <f t="shared" ref="AL12:AL29" si="2">SUM(S12:V12)</f>
         <v>1468.8000000000002</v>
       </c>
     </row>
@@ -4888,19 +4892,19 @@
         <v>172.3</v>
       </c>
       <c r="X13" s="2">
-        <f>+T13</f>
+        <f t="shared" si="1"/>
         <v>161.9</v>
       </c>
       <c r="Y13" s="2">
-        <f>+U13</f>
+        <f t="shared" si="1"/>
         <v>168.9</v>
       </c>
       <c r="Z13" s="2">
-        <f>+V13</f>
+        <f t="shared" si="1"/>
         <v>166.2</v>
       </c>
       <c r="AL13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>673.3</v>
       </c>
     </row>
@@ -4959,19 +4963,19 @@
         <v>112.6</v>
       </c>
       <c r="X14" s="2">
-        <f>+T14*0.9</f>
+        <f t="shared" ref="X14:Z15" si="3">+T14*0.9</f>
         <v>111.87</v>
       </c>
       <c r="Y14" s="2">
-        <f>+U14*0.9</f>
+        <f t="shared" si="3"/>
         <v>116.91000000000001</v>
       </c>
       <c r="Z14" s="2">
-        <f>+V14*0.9</f>
+        <f t="shared" si="3"/>
         <v>114.3</v>
       </c>
       <c r="AL14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>495.4</v>
       </c>
     </row>
@@ -5030,19 +5034,19 @@
         <v>98.5</v>
       </c>
       <c r="X15" s="2">
-        <f>+T15*0.9</f>
+        <f t="shared" si="3"/>
         <v>95.49</v>
       </c>
       <c r="Y15" s="2">
-        <f>+U15*0.9</f>
+        <f t="shared" si="3"/>
         <v>90.18</v>
       </c>
       <c r="Z15" s="2">
-        <f>+V15*0.9</f>
+        <f t="shared" si="3"/>
         <v>79.739999999999995</v>
       </c>
       <c r="AL15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>395.6</v>
       </c>
     </row>
@@ -5113,7 +5117,7 @@
         <v>73.099999999999994</v>
       </c>
       <c r="AL16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>392</v>
       </c>
     </row>
@@ -5184,7 +5188,7 @@
         <v>60.389999999999993</v>
       </c>
       <c r="AL17" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>285.60000000000002</v>
       </c>
     </row>
@@ -5255,7 +5259,7 @@
         <v>94.920000000000016</v>
       </c>
       <c r="AL18" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>328.2</v>
       </c>
     </row>
@@ -5314,19 +5318,19 @@
         <v>59.3</v>
       </c>
       <c r="X19" s="2">
-        <f>+T19</f>
+        <f t="shared" ref="X19:Z21" si="4">+T19</f>
         <v>62.7</v>
       </c>
       <c r="Y19" s="2">
-        <f>+U19</f>
+        <f t="shared" si="4"/>
         <v>66.3</v>
       </c>
       <c r="Z19" s="2">
-        <f>+V19</f>
+        <f t="shared" si="4"/>
         <v>64.5</v>
       </c>
       <c r="AL19" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>252.89999999999998</v>
       </c>
     </row>
@@ -5385,19 +5389,19 @@
         <v>60.2</v>
       </c>
       <c r="X20" s="2">
-        <f>+T20</f>
+        <f t="shared" si="4"/>
         <v>58.9</v>
       </c>
       <c r="Y20" s="2">
-        <f>+U20</f>
+        <f t="shared" si="4"/>
         <v>60.6</v>
       </c>
       <c r="Z20" s="2">
-        <f>+V20</f>
+        <f t="shared" si="4"/>
         <v>58.2</v>
       </c>
       <c r="AL20" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>235.7</v>
       </c>
     </row>
@@ -5456,19 +5460,19 @@
         <v>37.1</v>
       </c>
       <c r="X21" s="2">
-        <f>+T21</f>
+        <f t="shared" si="4"/>
         <v>45.6</v>
       </c>
       <c r="Y21" s="2">
-        <f>+U21</f>
+        <f t="shared" si="4"/>
         <v>41.2</v>
       </c>
       <c r="Z21" s="2">
-        <f>+V21</f>
+        <f t="shared" si="4"/>
         <v>37.1</v>
       </c>
       <c r="AL21" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>166.4</v>
       </c>
     </row>
@@ -5495,7 +5499,7 @@
       </c>
       <c r="N22" s="7"/>
       <c r="AL22" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5566,7 +5570,7 @@
         <v>41.713000000000001</v>
       </c>
       <c r="AL23" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>188</v>
       </c>
     </row>
@@ -5625,19 +5629,19 @@
         <v>58.3</v>
       </c>
       <c r="X24" s="2">
-        <f t="shared" ref="X24:X26" si="2">+T24*1.01</f>
+        <f t="shared" ref="X24:X26" si="5">+T24*1.01</f>
         <v>55.045000000000002</v>
       </c>
       <c r="Y24" s="2">
-        <f t="shared" ref="Y24:Y26" si="3">+U24*1.01</f>
+        <f t="shared" ref="Y24:Y26" si="6">+U24*1.01</f>
         <v>62.822000000000003</v>
       </c>
       <c r="Z24" s="2">
-        <f t="shared" ref="Z24:Z26" si="4">+V24*1.01</f>
+        <f t="shared" ref="Z24:Z26" si="7">+V24*1.01</f>
         <v>67.265999999999991</v>
       </c>
       <c r="AL24" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>238.5</v>
       </c>
     </row>
@@ -5696,19 +5700,19 @@
         <v>33.299999999999997</v>
       </c>
       <c r="X25" s="2">
+        <f t="shared" si="5"/>
+        <v>37.268999999999998</v>
+      </c>
+      <c r="Y25" s="2">
+        <f t="shared" si="6"/>
+        <v>38.582000000000001</v>
+      </c>
+      <c r="Z25" s="2">
+        <f t="shared" si="7"/>
+        <v>41.511000000000003</v>
+      </c>
+      <c r="AL25" s="2">
         <f t="shared" si="2"/>
-        <v>37.268999999999998</v>
-      </c>
-      <c r="Y25" s="2">
-        <f t="shared" si="3"/>
-        <v>38.582000000000001</v>
-      </c>
-      <c r="Z25" s="2">
-        <f t="shared" si="4"/>
-        <v>41.511000000000003</v>
-      </c>
-      <c r="AL25" s="2">
-        <f t="shared" si="1"/>
         <v>146.20000000000002</v>
       </c>
     </row>
@@ -5767,19 +5771,19 @@
         <v>32.299999999999997</v>
       </c>
       <c r="X26" s="2">
+        <f t="shared" si="5"/>
+        <v>35.753999999999998</v>
+      </c>
+      <c r="Y26" s="2">
+        <f t="shared" si="6"/>
+        <v>38.986000000000004</v>
+      </c>
+      <c r="Z26" s="2">
+        <f t="shared" si="7"/>
+        <v>36.865000000000002</v>
+      </c>
+      <c r="AL26" s="2">
         <f t="shared" si="2"/>
-        <v>35.753999999999998</v>
-      </c>
-      <c r="Y26" s="2">
-        <f t="shared" si="3"/>
-        <v>38.986000000000004</v>
-      </c>
-      <c r="Z26" s="2">
-        <f t="shared" si="4"/>
-        <v>36.865000000000002</v>
-      </c>
-      <c r="AL26" s="2">
-        <f t="shared" si="1"/>
         <v>145</v>
       </c>
     </row>
@@ -5840,15 +5844,15 @@
         <v>3243.2</v>
       </c>
       <c r="X28" s="2">
-        <f>+T28*0.9</f>
+        <f t="shared" ref="X28:Z29" si="8">+T28*0.9</f>
         <v>3407.31</v>
       </c>
       <c r="Y28" s="2">
-        <f>+U28*0.9</f>
+        <f t="shared" si="8"/>
         <v>3364.2000000000003</v>
       </c>
       <c r="Z28" s="2">
-        <f>+V28*0.9</f>
+        <f t="shared" si="8"/>
         <v>3163.86</v>
       </c>
       <c r="AH28" s="2">
@@ -5866,7 +5870,7 @@
         <v>15388.4</v>
       </c>
       <c r="AL28" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14692.8</v>
       </c>
     </row>
@@ -5927,15 +5931,15 @@
         <v>11.1</v>
       </c>
       <c r="X29" s="2">
-        <f>+T29*0.9</f>
+        <f t="shared" si="8"/>
         <v>9.629999999999999</v>
       </c>
       <c r="Y29" s="2">
-        <f>+U29*0.9</f>
+        <f t="shared" si="8"/>
         <v>11.879999999999999</v>
       </c>
       <c r="Z29" s="2">
-        <f>+V29*0.9</f>
+        <f t="shared" si="8"/>
         <v>11.43</v>
       </c>
       <c r="AH29" s="2">
@@ -5951,7 +5955,7 @@
         <v>38.5</v>
       </c>
       <c r="AL29" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>46.5</v>
       </c>
     </row>
@@ -5963,87 +5967,87 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9">
-        <f t="shared" ref="F30:Z30" si="5">+F28+F29</f>
+        <f t="shared" ref="F30:Z30" si="9">+F28+F29</f>
         <v>3623.5</v>
       </c>
       <c r="G30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>4430.3</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>4577.8</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>4536.6000000000004</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>4341.6000000000004</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>4191.7</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>4116.7999999999993</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>4078.2000000000003</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3918.6</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3941.9</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3837.3</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3663.4</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3796.6</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3751.2</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3528.1</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3254.2999999999997</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3416.94</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3376.0800000000004</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3175.29</v>
       </c>
       <c r="AH30" s="8">
@@ -6159,68 +6163,68 @@
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7">
-        <f t="shared" ref="F32:M32" si="6">+F30-F31</f>
+        <f t="shared" ref="F32:M32" si="10">+F30-F31</f>
         <v>706.40000000000009</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1127.3000000000002</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1327.7000000000003</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1574.1000000000004</v>
       </c>
       <c r="J32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1546.4000000000005</v>
       </c>
       <c r="K32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1771.1999999999998</v>
       </c>
       <c r="L32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1703.2999999999993</v>
       </c>
       <c r="M32" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1748.4</v>
       </c>
       <c r="N32" s="7"/>
       <c r="P32" s="2">
-        <f>+P30-P31</f>
+        <f t="shared" ref="P32:W32" si="11">+P30-P31</f>
         <v>1608.6</v>
       </c>
       <c r="Q32" s="2">
-        <f>+Q30-Q31</f>
+        <f t="shared" si="11"/>
         <v>1691.3000000000002</v>
       </c>
       <c r="R32" s="2">
-        <f>+R30-R31</f>
+        <f t="shared" si="11"/>
         <v>1596.5</v>
       </c>
       <c r="S32" s="2">
-        <f>+S30-S31</f>
+        <f t="shared" si="11"/>
         <v>1504</v>
       </c>
       <c r="T32" s="2">
-        <f>+T30-T31</f>
+        <f t="shared" si="11"/>
         <v>1445.4</v>
       </c>
       <c r="U32" s="2">
-        <f>+U30-U31</f>
+        <f t="shared" si="11"/>
         <v>1459.1999999999998</v>
       </c>
       <c r="V32" s="2">
-        <f>+V30-V31</f>
+        <f t="shared" si="11"/>
         <v>1215</v>
       </c>
       <c r="W32" s="2">
-        <f>+W30-W31</f>
+        <f t="shared" si="11"/>
         <v>1161.1999999999998</v>
       </c>
       <c r="X32" s="2">
@@ -6313,15 +6317,15 @@
         <v>222</v>
       </c>
       <c r="X33" s="2">
-        <f>+T33</f>
+        <f t="shared" ref="X33:Z34" si="12">+T33</f>
         <v>204.1</v>
       </c>
       <c r="Y33" s="2">
-        <f>+U33</f>
+        <f t="shared" si="12"/>
         <v>198.4</v>
       </c>
       <c r="Z33" s="2">
-        <f>+V33</f>
+        <f t="shared" si="12"/>
         <v>206.5</v>
       </c>
       <c r="AH33" s="2">
@@ -6397,15 +6401,15 @@
         <v>948.1</v>
       </c>
       <c r="X34" s="2">
-        <f>+T34</f>
+        <f t="shared" si="12"/>
         <v>1358</v>
       </c>
       <c r="Y34" s="2">
-        <f>+U34</f>
+        <f t="shared" si="12"/>
         <v>1003.4</v>
       </c>
       <c r="Z34" s="2">
-        <f>+V34</f>
+        <f t="shared" si="12"/>
         <v>1046.7</v>
       </c>
       <c r="AH34" s="2">
@@ -6432,35 +6436,35 @@
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7">
-        <f t="shared" ref="F35:M35" si="7">+F33+F34</f>
+        <f t="shared" ref="F35:M35" si="13">+F33+F34</f>
         <v>1516.2</v>
       </c>
       <c r="G35" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1370.6</v>
       </c>
       <c r="H35" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1352.5</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1207.0999999999999</v>
       </c>
       <c r="J35" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1350.1000000000001</v>
       </c>
       <c r="K35" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1057.5999999999999</v>
       </c>
       <c r="L35" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1143.7</v>
       </c>
       <c r="M35" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1192.2</v>
       </c>
       <c r="N35" s="7"/>
@@ -6469,27 +6473,27 @@
         <v>1240.2</v>
       </c>
       <c r="Q35" s="2">
-        <f t="shared" ref="Q35" si="8">+Q33+Q34</f>
+        <f t="shared" ref="Q35" si="14">+Q33+Q34</f>
         <v>1264.7</v>
       </c>
       <c r="R35" s="2">
-        <f t="shared" ref="R35:V35" si="9">+R33+R34</f>
+        <f t="shared" ref="R35:V35" si="15">+R33+R34</f>
         <v>1808.6</v>
       </c>
       <c r="S35" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>1217.2</v>
       </c>
       <c r="T35" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>1562.1</v>
       </c>
       <c r="U35" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>1201.8</v>
       </c>
       <c r="V35" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>1253.2</v>
       </c>
       <c r="W35" s="2">
@@ -6513,19 +6517,19 @@
         <v>3857.2</v>
       </c>
       <c r="AI35" s="2">
-        <f t="shared" ref="AI35:AL35" si="10">AI33+AI34</f>
+        <f t="shared" ref="AI35:AL35" si="16">AI33+AI34</f>
         <v>5210.2</v>
       </c>
       <c r="AJ35" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>4841.3</v>
       </c>
       <c r="AK35" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>5455.3</v>
       </c>
       <c r="AL35" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>5234.3</v>
       </c>
     </row>
@@ -6537,35 +6541,35 @@
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7">
-        <f t="shared" ref="F36:M36" si="11">+F32-F35</f>
+        <f t="shared" ref="F36:M36" si="17">+F32-F35</f>
         <v>-809.8</v>
       </c>
       <c r="G36" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>-243.29999999999973</v>
       </c>
       <c r="H36" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>-24.799999999999727</v>
       </c>
       <c r="I36" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>367.00000000000045</v>
       </c>
       <c r="J36" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>196.30000000000041</v>
       </c>
       <c r="K36" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>713.59999999999991</v>
       </c>
       <c r="L36" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>559.59999999999923</v>
       </c>
       <c r="M36" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>556.20000000000005</v>
       </c>
       <c r="N36" s="7"/>
@@ -6574,43 +6578,43 @@
         <v>368.39999999999986</v>
       </c>
       <c r="Q36" s="2">
-        <f t="shared" ref="Q36" si="12">+Q32-Q35</f>
+        <f t="shared" ref="Q36" si="18">+Q32-Q35</f>
         <v>426.60000000000014</v>
       </c>
       <c r="R36" s="2">
-        <f t="shared" ref="R36:Z36" si="13">+R32-R35</f>
+        <f t="shared" ref="R36:Z36" si="19">+R32-R35</f>
         <v>-212.09999999999991</v>
       </c>
       <c r="S36" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>286.79999999999995</v>
       </c>
       <c r="T36" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-116.69999999999982</v>
       </c>
       <c r="U36" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>257.39999999999986</v>
       </c>
       <c r="V36" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-38.200000000000045</v>
       </c>
       <c r="W36" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-8.9000000000000909</v>
       </c>
       <c r="X36" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-332.00159999999983</v>
       </c>
       <c r="Y36" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>13.588800000000219</v>
       </c>
       <c r="Z36" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-110.0956000000001</v>
       </c>
       <c r="AH36" s="2">
@@ -6618,19 +6622,19 @@
         <v>-60.5</v>
       </c>
       <c r="AI36" s="2">
-        <f t="shared" ref="AI36:AL36" si="14">AI32-AI35</f>
+        <f t="shared" ref="AI36:AL36" si="20">AI32-AI35</f>
         <v>365.30000000000018</v>
       </c>
       <c r="AJ36" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>1655.699999999998</v>
       </c>
       <c r="AK36" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>983.30000000000018</v>
       </c>
       <c r="AL36" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>389.29999999999836</v>
       </c>
     </row>
@@ -6734,65 +6738,65 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7">
-        <f t="shared" ref="F38:P38" si="15">+F36+F37</f>
+        <f t="shared" ref="F38:P38" si="21">+F36+F37</f>
         <v>-942.19999999999993</v>
       </c>
       <c r="G38" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-418.39999999999975</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-196.09999999999971</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>209.30000000000044</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>70.000000000000426</v>
       </c>
       <c r="K38" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>533.69999999999993</v>
       </c>
       <c r="L38" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>400.19999999999925</v>
       </c>
       <c r="M38" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>423.6</v>
       </c>
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
       <c r="P38" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>224.69999999999987</v>
       </c>
       <c r="Q38" s="2">
-        <f t="shared" ref="Q38:V38" si="16">+Q36+Q37</f>
+        <f t="shared" ref="Q38:V38" si="22">+Q36+Q37</f>
         <v>285.10000000000014</v>
       </c>
       <c r="R38" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-352.99999999999989</v>
       </c>
       <c r="S38" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>148.39999999999995</v>
       </c>
       <c r="T38" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-262.49999999999983</v>
       </c>
       <c r="U38" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>111.79999999999987</v>
       </c>
       <c r="V38" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-158.40000000000003</v>
       </c>
       <c r="W38" s="2">
@@ -6816,19 +6820,19 @@
         <v>-558.29999999999995</v>
       </c>
       <c r="AI38" s="2">
-        <f t="shared" ref="AI38:AL38" si="17">AI36+AI37</f>
+        <f t="shared" ref="AI38:AL38" si="23">AI36+AI37</f>
         <v>-270.89999999999986</v>
       </c>
       <c r="AJ38" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>1063.2999999999979</v>
       </c>
       <c r="AK38" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>410.20000000000016</v>
       </c>
       <c r="AL38" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>-160.70000000000164</v>
       </c>
     </row>
@@ -6921,81 +6925,81 @@
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7">
-        <f t="shared" ref="F40:P40" si="18">+F38-F39</f>
+        <f t="shared" ref="F40:P40" si="24">+F38-F39</f>
         <v>-942.19999999999993</v>
       </c>
       <c r="G40" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>-1014.6999999999997</v>
       </c>
       <c r="H40" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>-256.1999999999997</v>
       </c>
       <c r="I40" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>209.30000000000044</v>
       </c>
       <c r="J40" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>10.100000000000428</v>
       </c>
       <c r="K40" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>405.39999999999992</v>
       </c>
       <c r="L40" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>324.79999999999927</v>
       </c>
       <c r="M40" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>350.40000000000003</v>
       </c>
       <c r="N40" s="7"/>
       <c r="O40" s="7"/>
       <c r="P40" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>155.69999999999987</v>
       </c>
       <c r="Q40" s="2">
-        <f t="shared" ref="Q40:R40" si="19">+Q38+Q39</f>
+        <f t="shared" ref="Q40:R40" si="25">+Q38+Q39</f>
         <v>143.60000000000014</v>
       </c>
       <c r="R40" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>-352.99999999999989</v>
       </c>
       <c r="S40" s="2">
-        <f>+S38+S39</f>
+        <f t="shared" ref="S40:Z40" si="26">+S38+S39</f>
         <v>148.39999999999995</v>
       </c>
       <c r="T40" s="2">
-        <f>+T38+T39</f>
+        <f t="shared" si="26"/>
         <v>-327.89999999999986</v>
       </c>
       <c r="U40" s="2">
-        <f>+U38+U39</f>
+        <f t="shared" si="26"/>
         <v>-33.800000000000125</v>
       </c>
       <c r="V40" s="2">
-        <f>+V38+V39</f>
+        <f t="shared" si="26"/>
         <v>-158.40000000000003</v>
       </c>
       <c r="W40" s="2">
-        <f>+W38+W39</f>
+        <f t="shared" si="26"/>
         <v>-120.40000000000009</v>
       </c>
       <c r="X40" s="2">
-        <f>+X38+X39</f>
+        <f t="shared" si="26"/>
         <v>-443.50159999999983</v>
       </c>
       <c r="Y40" s="2">
-        <f>+Y38+Y39</f>
+        <f t="shared" si="26"/>
         <v>-97.911199999999781</v>
       </c>
       <c r="Z40" s="2">
-        <f>+Z38+Z39</f>
+        <f t="shared" si="26"/>
         <v>-221.5956000000001</v>
       </c>
       <c r="AH40" s="2">
@@ -7027,80 +7031,80 @@
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5">
-        <f t="shared" ref="F41:M41" si="20">+F40/F42</f>
+        <f t="shared" ref="F41:M41" si="27">+F40/F42</f>
         <v>-1.1027621722846441</v>
       </c>
       <c r="G41" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-0.8403312629399583</v>
       </c>
       <c r="H41" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-0.21194573130377209</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.17260432129308961</v>
       </c>
       <c r="J41" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>8.3512485530018409E-3</v>
       </c>
       <c r="K41" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.33418514549501271</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.26686385670856899</v>
       </c>
       <c r="M41" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.28766111156719487</v>
       </c>
       <c r="N41" s="5"/>
       <c r="P41" s="1">
-        <f>+P40/P42</f>
+        <f t="shared" ref="P41:Z41" si="28">+P40/P42</f>
         <v>0.12937266306605724</v>
       </c>
       <c r="Q41" s="1">
-        <f>+Q40/Q42</f>
+        <f t="shared" si="28"/>
         <v>0.11891354753229559</v>
       </c>
       <c r="R41" s="1">
-        <f>+R40/R42</f>
+        <f t="shared" si="28"/>
         <v>-0.29414215482043155</v>
       </c>
       <c r="S41" s="1">
-        <f>+S40/S42</f>
+        <f t="shared" si="28"/>
         <v>0.12269532864820169</v>
       </c>
       <c r="T41" s="1">
-        <f>+T40/T42</f>
+        <f t="shared" si="28"/>
         <v>-0.27529174712450666</v>
       </c>
       <c r="U41" s="1">
-        <f>+U40/U42</f>
+        <f t="shared" si="28"/>
         <v>-2.8157280906364646E-2</v>
       </c>
       <c r="V41" s="1">
-        <f>+V40/V42</f>
+        <f t="shared" si="28"/>
         <v>-0.13270777479892765</v>
       </c>
       <c r="W41" s="1">
-        <f>+W40/W42</f>
+        <f t="shared" si="28"/>
         <v>-0.10097282791009735</v>
       </c>
       <c r="X41" s="1">
-        <f>+X40/X42</f>
+        <f t="shared" si="28"/>
         <v>-0.37194028849379385</v>
       </c>
       <c r="Y41" s="1">
-        <f>+Y40/Y42</f>
+        <f t="shared" si="28"/>
         <v>-8.2112713854411087E-2</v>
       </c>
       <c r="Z41" s="1">
-        <f>+Z40/Z42</f>
+        <f t="shared" si="28"/>
         <v>-0.18583998658168407</v>
       </c>
       <c r="AH41" s="1">
@@ -7108,19 +7112,19 @@
         <v>-0.92864271457085812</v>
       </c>
       <c r="AI41" s="1">
-        <f t="shared" ref="AI41:AL41" si="21">AI40/AI42</f>
+        <f t="shared" ref="AI41:AL41" si="29">AI40/AI42</f>
         <v>-0.22410655195234933</v>
       </c>
       <c r="AJ41" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>0.27000164284540651</v>
       </c>
       <c r="AK41" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>0.33987902891706034</v>
       </c>
       <c r="AL41" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>-0.13466856616106732</v>
       </c>
     </row>
@@ -7230,11 +7234,11 @@
         <v>-0.1010448353392408</v>
       </c>
       <c r="T45" s="42">
-        <f t="shared" ref="T45" si="22">+T30/P30-1</f>
+        <f t="shared" ref="T45" si="30">+T30/P30-1</f>
         <v>-3.113356811106005E-2</v>
       </c>
       <c r="U45" s="42">
-        <f t="shared" ref="U45" si="23">+U30/Q30-1</f>
+        <f t="shared" ref="U45" si="31">+U30/Q30-1</f>
         <v>-4.8377685887516231E-2</v>
       </c>
       <c r="V45" s="42">
@@ -7246,15 +7250,15 @@
         <v>-0.11167221706611352</v>
       </c>
       <c r="X45" s="42">
-        <f t="shared" ref="X45:Z45" si="24">+X30/T30-1</f>
+        <f t="shared" ref="X45:Z45" si="32">+X30/T30-1</f>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="Y45" s="42">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>-9.9999999999999867E-2</v>
       </c>
       <c r="Z45" s="42">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="AI45" s="42">
@@ -7262,15 +7266,15 @@
         <v>0.49726268206931179</v>
       </c>
       <c r="AJ45" s="42">
-        <f t="shared" ref="AJ45:AL45" si="25">AJ30/AI30-1</f>
+        <f t="shared" ref="AJ45:AL45" si="33">AJ30/AI30-1</f>
         <v>-9.0773385216618374E-2</v>
       </c>
       <c r="AK45" s="42">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>-5.1393680016233456E-2</v>
       </c>
       <c r="AL45" s="42">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>-4.4571495245318227E-2</v>
       </c>
     </row>
@@ -7279,51 +7283,51 @@
         <v>22</v>
       </c>
       <c r="F46" s="4">
-        <f t="shared" ref="F46:M46" si="26">+F32/F30</f>
+        <f t="shared" ref="F46:M46" si="34">+F32/F30</f>
         <v>0.19494963433144752</v>
       </c>
       <c r="G46" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.254452294427014</v>
       </c>
       <c r="H46" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.29003014548473072</v>
       </c>
       <c r="I46" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.34697791297447433</v>
       </c>
       <c r="J46" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.35618205269946573</v>
       </c>
       <c r="K46" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.42254932366343007</v>
       </c>
       <c r="L46" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.41374368441507958</v>
       </c>
       <c r="M46" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.4287185523024864</v>
       </c>
       <c r="R46" s="42">
-        <f t="shared" ref="R46:U46" si="27">+R32/R30</f>
+        <f t="shared" ref="R46:U46" si="35">+R32/R30</f>
         <v>0.41604774190185806</v>
       </c>
       <c r="S46" s="42">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v>0.410547578751979</v>
       </c>
       <c r="T46" s="42">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v>0.38070905547068434</v>
       </c>
       <c r="U46" s="42">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v>0.38899552143314137</v>
       </c>
       <c r="V46" s="42">
@@ -7335,15 +7339,15 @@
         <v>0.35682020711059209</v>
       </c>
       <c r="X46" s="42">
-        <f t="shared" ref="X46:Z46" si="28">+X32/X30</f>
+        <f t="shared" ref="X46:Z46" si="36">+X32/X30</f>
         <v>0.36000000000000004</v>
       </c>
       <c r="Y46" s="42">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>0.36</v>
       </c>
       <c r="Z46" s="42">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>0.36</v>
       </c>
       <c r="AH46" s="42">
@@ -7744,15 +7748,15 @@
         <v>45330.000000000007</v>
       </c>
       <c r="U58" s="2">
-        <f t="shared" ref="U58:W58" si="29">SUM(U49:U57)</f>
+        <f t="shared" ref="U58:W58" si="37">SUM(U49:U57)</f>
         <v>0</v>
       </c>
       <c r="V58" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>41500.9</v>
       </c>
       <c r="W58" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>38474.9</v>
       </c>
       <c r="AJ58" s="8">
@@ -8058,15 +8062,15 @@
         <v>45330</v>
       </c>
       <c r="U68" s="2">
-        <f t="shared" ref="U68:W68" si="30">SUM(U60:U67)</f>
+        <f t="shared" ref="U68:W68" si="38">SUM(U60:U67)</f>
         <v>0</v>
       </c>
       <c r="V68" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>41500.899999999994</v>
       </c>
       <c r="W68" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>38474.9</v>
       </c>
       <c r="AJ68" s="8">
@@ -8153,31 +8157,31 @@
       <c r="M73" s="7"/>
       <c r="N73" s="7"/>
       <c r="P73" s="2">
-        <f t="shared" ref="P73:W73" si="31">+P40</f>
+        <f t="shared" ref="P73:V73" si="39">+P40</f>
         <v>155.69999999999987</v>
       </c>
       <c r="Q73" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>143.60000000000014</v>
       </c>
       <c r="R73" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>-352.99999999999989</v>
       </c>
       <c r="S73" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>148.39999999999995</v>
       </c>
       <c r="T73" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>-327.89999999999986</v>
       </c>
       <c r="U73" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>-33.800000000000125</v>
       </c>
       <c r="V73" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>-158.40000000000003</v>
       </c>
       <c r="W73" s="2">
@@ -8411,31 +8415,31 @@
       <c r="M82" s="7"/>
       <c r="N82" s="7"/>
       <c r="P82" s="2">
-        <f t="shared" ref="P82:V82" si="32">SUM(P74:P81)</f>
+        <f t="shared" ref="P82:V82" si="40">SUM(P74:P81)</f>
         <v>0</v>
       </c>
       <c r="Q82" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="R82" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="S82" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="T82" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U82" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="V82" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="W82" s="2">
